--- a/fundraiser_forms/004_opt_out_fundraiser_form--fundraiser_forms.xlsx
+++ b/fundraiser_forms/004_opt_out_fundraiser_form--fundraiser_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>opt_out_fundraiser_form_1</t>
+          <t>fundraiser_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fundraiser_name</t>
+          <t>donor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>donor_name</t>
+          <t>donation_amount</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Donor</t>
+          <t>Donation Amount</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,35 +589,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Donation</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>donor_type</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Donation</t>
+          <t>Type of Donor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,40 +630,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>fundraiser_type</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Type of Fundraiser</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>event_date</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Event Date</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,40 +676,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>donor_type</t>
+          <t>event_time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Type of Donor</t>
+          <t>Event Time</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fundraiser_type</t>
+          <t>donor_email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Type of Fundraiser</t>
+          <t>Donor Email</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>donor_phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Donor Phone</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>donor_address</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Donor Address</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>donor_city</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Donor City</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>donor_state</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Donor State</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,269 +819,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>donor_zip</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Donor Zip</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>zip</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Zip</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Donation</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>donor_type</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Type of Donor</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>fundraiser_type</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Type of Fundraiser</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +845,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,85 +873,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>amount_choices</t>
+          <t>donation_amount_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option':_'$100'}</t>
+          <t>$100</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option': '$100'}</t>
+          <t>$100</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>amount_choices</t>
+          <t>donation_amount_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option':_'$250'}</t>
+          <t>$250</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option': '$250'}</t>
+          <t>$250</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>amount_choices</t>
+          <t>donation_amount_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option':_'$500'}</t>
+          <t>$500</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option': '$500'}</t>
+          <t>$500</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>amount_choices</t>
+          <t>donation_amount_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option':_'$1000'}</t>
+          <t>$1000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option': '$1000'}</t>
+          <t>$1000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>amount_choices</t>
+          <t>donation_amount_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option':_'$5000'}</t>
+          <t>$5000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option': '$5000'}</t>
+          <t>$5000</t>
         </is>
       </c>
     </row>
@@ -1216,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option':_'individual'}</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option': 'Individual'}</t>
+          <t>Individual</t>
         </is>
       </c>
     </row>
@@ -1233,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -1250,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option':_'school'}</t>
+          <t>school</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option': 'School'}</t>
+          <t>School</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option':_'organization'}</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option': 'Organization'}</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option':_'fundraiser_1'}</t>
+          <t>fundraiser_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option': 'Fundraiser 1'}</t>
+          <t>Fundraiser 1</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option':_'fundraiser_2'}</t>
+          <t>fundraiser_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option': 'Fundraiser 2'}</t>
+          <t>Fundraiser 2</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option':_'fundraiser_3'}</t>
+          <t>fundraiser_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option': 'Fundraiser 3'}</t>
+          <t>Fundraiser 3</t>
         </is>
       </c>
     </row>
@@ -1335,233 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option':_'fundraiser_4'}</t>
+          <t>fundraiser_4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option': 'Fundraiser 4'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>amount_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'option':_'$100'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'option': '$100'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>amount_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'option':_'$250'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'option': '$250'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>amount_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'option':_'$500'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'option': '$500'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>amount_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'option':_'$1000'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'option': '$1000'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>amount_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'option':_'$5000'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'option': '$5000'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>donor_type_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'option':_'individual'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'option': 'Individual'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>donor_type_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'option':_'parent'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'option': 'Parent'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>donor_type_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'option':_'school'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'option': 'School'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>donor_type_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'option':_'organization'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'option': 'Organization'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>fundraiser_type_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'option':_'fundraiser_1'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'option': 'Fundraiser 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>fundraiser_type_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'option':_'fundraiser_2'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'option': 'Fundraiser 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>fundraiser_type_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'option':_'fundraiser_3'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'option': 'Fundraiser 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>fundraiser_type_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'option':_'fundraiser_4'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'option': 'Fundraiser 4'}</t>
+          <t>Fundraiser 4</t>
         </is>
       </c>
     </row>
